--- a/artfynd/A 21629-2024 artfynd.xlsx
+++ b/artfynd/A 21629-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>113680629</v>
       </c>
       <c r="B2" t="n">
-        <v>93229</v>
+        <v>93296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680628</v>
       </c>
       <c r="B3" t="n">
-        <v>93198</v>
+        <v>93265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,6 +884,113 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>38725</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storån, Lidsjöberg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>507781</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7134330</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2007-10-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2007-10-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inv faunapassager</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Bergström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Tomas Bergström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21629-2024 artfynd.xlsx
+++ b/artfynd/A 21629-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680628</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,8 +1006,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/38725</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>